--- a/packages/calculators/src/modules/test/6.4-crop-burning.xlsx
+++ b/packages/calculators/src/modules/test/6.4-crop-burning.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators/packages/calculators/src/modules/test/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mackcheesman/Desktop/Work/EAP/Code/emissions-calculators/packages/calculators/src/modules/test/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BDEC4D-F64F-C340-A7A8-378E7C2BC920}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DDC6EBC-6195-2340-AC40-1993A59BA445}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51240" yWindow="18000" windowWidth="28800" windowHeight="23520" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
+    <workbookView xWindow="20" yWindow="600" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.4.1.1" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="53">
   <si>
     <t>Method 1</t>
   </si>
@@ -47,9 +47,6 @@
     <t>Cn2o</t>
   </si>
   <si>
-    <t>Average yield per hectare in kg</t>
-  </si>
-  <si>
     <t>En2o</t>
   </si>
   <si>
@@ -531,6 +528,12 @@
   </si>
   <si>
     <t>EFn2o</t>
+  </si>
+  <si>
+    <t>Average yield per hectare in t</t>
+  </si>
+  <si>
+    <t>Total production yield (kg)</t>
   </si>
 </sst>
 </file>
@@ -992,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:21">
@@ -1001,13 +1004,15 @@
       <c r="N2" s="1"/>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:21" ht="34">
+    <row r="3" spans="1:21" ht="51">
       <c r="D3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>5</v>
-      </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7" t="s">
-        <v>6</v>
       </c>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
@@ -1015,64 +1020,64 @@
       <c r="J3" s="7"/>
       <c r="K3" s="7"/>
       <c r="L3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="R3" s="1"/>
     </row>
     <row r="4" spans="1:21" ht="34">
       <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="C4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="I4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J4" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L4" t="s">
+        <v>46</v>
+      </c>
+      <c r="M4" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" t="s">
+        <v>45</v>
+      </c>
+      <c r="O4" t="s">
+        <v>44</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q4" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>11</v>
-      </c>
-      <c r="G4" t="s">
-        <v>39</v>
-      </c>
-      <c r="I4" t="s">
-        <v>13</v>
-      </c>
-      <c r="J4" t="s">
-        <v>40</v>
-      </c>
-      <c r="K4" t="s">
-        <v>14</v>
-      </c>
-      <c r="L4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M4" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" t="s">
-        <v>46</v>
-      </c>
-      <c r="O4" t="s">
-        <v>45</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="S4" s="6" t="s">
         <v>1</v>
@@ -1080,23 +1085,23 @@
     </row>
     <row r="5" spans="1:21">
       <c r="A5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B5">
         <v>50</v>
       </c>
       <c r="C5">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D5" s="12">
         <v>0.2</v>
       </c>
       <c r="E5" s="12">
-        <f>IF(ISBLANK(#REF!), "", B5*C5)</f>
+        <f>IF(ISBLANK(A5), "", B5*(C5 * 1000))</f>
         <v>100000</v>
       </c>
       <c r="F5" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A5, $S$22:$AA$39, 2, FALSE))</f>
+        <f>IF(ISBLANK(A5), "", VLOOKUP($A5, $S$22:$AA$39, 2, FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="G5" s="12">
@@ -1120,7 +1125,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L5">
-        <f>IF(ISBLANK(#REF!),"", (E5*F5*H5*I5*J5*D5))</f>
+        <f>IF(ISBLANK(A5),"", (E5*F5*H5*I5*J5*D5))</f>
         <v>800</v>
       </c>
       <c r="M5">
@@ -1146,23 +1151,23 @@
     </row>
     <row r="6" spans="1:21">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B6">
         <v>50</v>
       </c>
       <c r="C6">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D6">
         <v>0.4</v>
       </c>
       <c r="E6" s="12">
-        <f>IF(ISBLANK(#REF!), "", B6*C6)</f>
+        <f t="shared" ref="E6:E22" si="0">IF(ISBLANK(A6), "", B6*(C6 * 1000))</f>
         <v>100000</v>
       </c>
       <c r="F6" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A6, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" ref="F6:F22" si="1">IF(ISBLANK(A6), "", VLOOKUP($A6, $S$22:$AA$39, 2, FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="G6" s="12">
@@ -1170,7 +1175,7 @@
         <v>1</v>
       </c>
       <c r="H6" s="12">
-        <f t="shared" ref="H6:H22" si="0">IF(G6="n/a", 0, G6)</f>
+        <f t="shared" ref="H6:H22" si="2">IF(G6="n/a", 0, G6)</f>
         <v>1</v>
       </c>
       <c r="I6" s="12">
@@ -1186,7 +1191,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L6">
-        <f>IF(ISBLANK(#REF!),"", (E6*F6*H6*I6*J6*D6))</f>
+        <f t="shared" ref="L6:L22" si="3">IF(ISBLANK(A6),"", (E6*F6*H6*I6*J6*D6))</f>
         <v>1600</v>
       </c>
       <c r="M6">
@@ -1206,11 +1211,11 @@
         <v>2.986666666666667E-3</v>
       </c>
       <c r="Q6">
-        <f t="shared" ref="Q6:Q22" si="1">L6*K6*$T$9*$T$8/1000</f>
+        <f t="shared" ref="Q6:Q22" si="4">L6*K6*$T$9*$T$8/1000</f>
         <v>9.554285714285714E-5</v>
       </c>
       <c r="S6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="T6">
         <f>16/12</f>
@@ -1219,23 +1224,23 @@
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7">
         <v>50</v>
       </c>
       <c r="C7">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D7">
         <v>0.2</v>
       </c>
       <c r="E7" s="12">
-        <f>IF(ISBLANK(#REF!), "", B7*C7)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F7" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A7, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.31</v>
       </c>
       <c r="G7" s="12">
@@ -1243,7 +1248,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I7" s="12">
@@ -1259,7 +1264,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L7">
-        <f>IF(ISBLANK(#REF!),"", (E7*F7*H7*I7*J7*D7))</f>
+        <f t="shared" si="3"/>
         <v>16768</v>
       </c>
       <c r="M7">
@@ -1279,11 +1284,11 @@
         <v>3.2865279999999997E-2</v>
       </c>
       <c r="Q7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.4018048E-3</v>
       </c>
       <c r="S7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T7">
         <v>3.5000000000000001E-3</v>
@@ -1291,23 +1296,23 @@
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8">
         <v>50</v>
       </c>
       <c r="C8">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D8">
         <v>0.4</v>
       </c>
       <c r="E8" s="12">
-        <f>IF(ISBLANK(#REF!), "", B8*C8)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F8" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A8, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.31</v>
       </c>
       <c r="G8" s="12">
@@ -1315,7 +1320,7 @@
         <v>1</v>
       </c>
       <c r="H8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I8" s="12">
@@ -1331,7 +1336,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L8">
-        <f>IF(ISBLANK(#REF!),"", (E8*F8*H8*I8*J8*D8))</f>
+        <f t="shared" si="3"/>
         <v>33536</v>
       </c>
       <c r="M8">
@@ -1351,7 +1356,7 @@
         <v>6.5730559999999993E-2</v>
       </c>
       <c r="Q8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.8036096000000001E-3</v>
       </c>
       <c r="S8" s="2" t="s">
@@ -1364,23 +1369,23 @@
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9">
         <v>50</v>
       </c>
       <c r="C9">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D9">
         <v>0.2</v>
       </c>
       <c r="E9" s="12">
-        <f>IF(ISBLANK(#REF!), "", B9*C9)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F9" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A9, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.34</v>
       </c>
       <c r="G9" s="12" t="str">
@@ -1388,7 +1393,7 @@
         <v>n/a</v>
       </c>
       <c r="H9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I9" s="12">
@@ -1404,7 +1409,7 @@
         <v>0.02</v>
       </c>
       <c r="L9">
-        <f>IF(ISBLANK(#REF!),"", (E9*F9*H9*I9*J9*D9))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M9">
@@ -1424,11 +1429,11 @@
         <v>0</v>
       </c>
       <c r="Q9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="T9" s="2">
         <v>7.6E-3</v>
@@ -1436,23 +1441,23 @@
     </row>
     <row r="10" spans="1:21">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10">
         <v>50</v>
       </c>
       <c r="C10">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D10">
         <v>0.1</v>
       </c>
       <c r="E10" s="12">
-        <f>IF(ISBLANK(#REF!), "", B10*C10)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F10" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A10, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.34</v>
       </c>
       <c r="G10" s="12" t="str">
@@ -1460,7 +1465,7 @@
         <v>n/a</v>
       </c>
       <c r="H10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I10" s="12">
@@ -1476,7 +1481,7 @@
         <v>0.02</v>
       </c>
       <c r="L10">
-        <f>IF(ISBLANK(#REF!),"", (E10*F10*H10*I10*J10*D10))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M10">
@@ -1496,29 +1501,29 @@
         <v>0</v>
       </c>
       <c r="Q10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:21">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11">
         <v>50</v>
       </c>
       <c r="C11">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D11">
         <v>0.3</v>
       </c>
       <c r="E11" s="12">
-        <f>IF(ISBLANK(#REF!), "", B11*C11)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F11" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A11, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.9</v>
       </c>
       <c r="G11" s="12" t="str">
@@ -1526,7 +1531,7 @@
         <v>n/a</v>
       </c>
       <c r="H11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I11" s="12">
@@ -1542,7 +1547,7 @@
         <v>0.01</v>
       </c>
       <c r="L11">
-        <f>IF(ISBLANK(#REF!),"", (E11*F11*H11*I11*J11*D11))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M11">
@@ -1562,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="Q11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S11" s="2"/>
@@ -1570,23 +1575,23 @@
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>50</v>
       </c>
       <c r="C12">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D12">
         <v>0.3</v>
       </c>
       <c r="E12" s="12">
-        <f>IF(ISBLANK(#REF!), "", B12*C12)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F12" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A12, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="G12" s="12" t="str">
@@ -1594,7 +1599,7 @@
         <v>n/a</v>
       </c>
       <c r="H12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I12" s="12">
@@ -1610,7 +1615,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L12">
-        <f>IF(ISBLANK(#REF!),"", (E12*F12*H12*I12*J12*D12))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M12">
@@ -1630,7 +1635,7 @@
         <v>0</v>
       </c>
       <c r="Q12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="S12" s="2"/>
@@ -1638,23 +1643,23 @@
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>50</v>
       </c>
       <c r="C13">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D13">
         <v>0.3</v>
       </c>
       <c r="E13" s="12">
-        <f>IF(ISBLANK(#REF!), "", B13*C13)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F13" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A13, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.34</v>
       </c>
       <c r="G13" s="12" t="str">
@@ -1662,7 +1667,7 @@
         <v>n/a</v>
       </c>
       <c r="H13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="I13" s="12">
@@ -1678,7 +1683,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L13">
-        <f>IF(ISBLANK(#REF!),"", (E13*F13*H13*I13*J13*D13))</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="M13">
@@ -1698,29 +1703,29 @@
         <v>0</v>
       </c>
       <c r="Q13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B14">
         <v>50</v>
       </c>
       <c r="C14">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D14">
         <v>0.3</v>
       </c>
       <c r="E14" s="12">
-        <f>IF(ISBLANK(#REF!), "", B14*C14)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F14" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A14, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.07</v>
       </c>
       <c r="G14" s="12">
@@ -1728,7 +1733,7 @@
         <v>0.5</v>
       </c>
       <c r="H14" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I14" s="12">
@@ -1744,7 +1749,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="L14">
-        <f>IF(ISBLANK(#REF!),"", (E14*F14*H14*I14*J14*D14))</f>
+        <f t="shared" si="3"/>
         <v>10914</v>
       </c>
       <c r="M14">
@@ -1764,7 +1769,7 @@
         <v>2.1391440000000005E-2</v>
       </c>
       <c r="Q14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.0855094857142858E-3</v>
       </c>
       <c r="S14" s="2"/>
@@ -1773,23 +1778,23 @@
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15">
         <v>50</v>
       </c>
       <c r="C15">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D15">
         <v>0.3</v>
       </c>
       <c r="E15" s="12">
-        <f>IF(ISBLANK(#REF!), "", B15*C15)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F15" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A15, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>2.08</v>
       </c>
       <c r="G15" s="12">
@@ -1797,7 +1802,7 @@
         <v>0.5</v>
       </c>
       <c r="H15" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I15" s="12">
@@ -1813,7 +1818,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="L15">
-        <f>IF(ISBLANK(#REF!),"", (E15*F15*H15*I15*J15*D15))</f>
+        <f t="shared" si="3"/>
         <v>25459.200000000001</v>
       </c>
       <c r="M15">
@@ -1833,7 +1838,7 @@
         <v>4.7523840000000005E-2</v>
       </c>
       <c r="Q15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>2.7365002971428574E-3</v>
       </c>
       <c r="S15" s="2"/>
@@ -1842,23 +1847,23 @@
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B16">
         <v>50</v>
       </c>
       <c r="C16">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D16">
         <v>0.3</v>
       </c>
       <c r="E16" s="12">
-        <f>IF(ISBLANK(#REF!), "", B16*C16)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F16" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A16, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.24</v>
       </c>
       <c r="G16" s="12">
@@ -1866,7 +1871,7 @@
         <v>0.5</v>
       </c>
       <c r="H16" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I16" s="12">
@@ -1882,7 +1887,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L16">
-        <f>IF(ISBLANK(#REF!),"", (E16*F16*H16*I16*J16*D16))</f>
+        <f t="shared" si="3"/>
         <v>13912.8</v>
       </c>
       <c r="M16">
@@ -1902,7 +1907,7 @@
         <v>2.597056E-2</v>
       </c>
       <c r="Q16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.1631100800000001E-3</v>
       </c>
       <c r="S16" s="2"/>
@@ -1911,23 +1916,23 @@
     </row>
     <row r="17" spans="1:27">
       <c r="A17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B17">
         <v>50</v>
       </c>
       <c r="C17">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D17">
         <v>0.3</v>
       </c>
       <c r="E17" s="12">
-        <f>IF(ISBLANK(#REF!), "", B17*C17)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F17" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A17, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>0.81</v>
       </c>
       <c r="G17" s="12">
@@ -1935,7 +1940,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="I17" s="12">
@@ -1951,7 +1956,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L17">
-        <f>IF(ISBLANK(#REF!),"", (E17*F17*H17*I17*J17*D17))</f>
+        <f t="shared" si="3"/>
         <v>16524</v>
       </c>
       <c r="M17">
@@ -1971,29 +1976,29 @@
         <v>3.2387039999999999E-2</v>
       </c>
       <c r="Q17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>9.8671885714285705E-4</v>
       </c>
     </row>
     <row r="18" spans="1:27">
       <c r="A18" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B18">
         <v>50</v>
       </c>
       <c r="C18">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D18">
         <v>0.3</v>
       </c>
       <c r="E18" s="12">
-        <f>IF(ISBLANK(#REF!), "", B18*C18)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F18" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A18, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.42</v>
       </c>
       <c r="G18" s="12">
@@ -2001,7 +2006,7 @@
         <v>0.5</v>
       </c>
       <c r="H18" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I18" s="12">
@@ -2017,7 +2022,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L18">
-        <f>IF(ISBLANK(#REF!),"", (E18*F18*H18*I18*J18*D18))</f>
+        <f t="shared" si="3"/>
         <v>15932.4</v>
       </c>
       <c r="M18">
@@ -2037,7 +2042,7 @@
         <v>2.974048E-2</v>
       </c>
       <c r="Q18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.1416702628571427E-3</v>
       </c>
       <c r="S18" s="2"/>
@@ -2045,23 +2050,23 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B19">
         <v>50</v>
       </c>
       <c r="C19">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D19">
         <v>0.3</v>
       </c>
       <c r="E19" s="12">
-        <f>IF(ISBLANK(#REF!), "", B19*C19)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F19" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A19, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.24</v>
       </c>
       <c r="G19" s="12">
@@ -2069,7 +2074,7 @@
         <v>0.5</v>
       </c>
       <c r="H19" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I19" s="12">
@@ -2085,7 +2090,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="L19">
-        <f>IF(ISBLANK(#REF!),"", (E19*F19*H19*I19*J19*D19))</f>
+        <f t="shared" si="3"/>
         <v>13912.8</v>
       </c>
       <c r="M19">
@@ -2105,7 +2110,7 @@
         <v>2.597056E-2</v>
       </c>
       <c r="Q19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.1631100800000001E-3</v>
       </c>
       <c r="S19" s="2"/>
@@ -2113,23 +2118,23 @@
     </row>
     <row r="20" spans="1:27">
       <c r="A20" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>50</v>
       </c>
       <c r="C20">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D20">
         <v>0.3</v>
       </c>
       <c r="E20" s="12">
-        <f>IF(ISBLANK(#REF!), "", B20*C20)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F20" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A20, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="G20" s="12">
@@ -2137,7 +2142,7 @@
         <v>0.5</v>
       </c>
       <c r="H20" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I20" s="12">
@@ -2153,7 +2158,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="L20">
-        <f>IF(ISBLANK(#REF!),"", (E20*F20*H20*I20*J20*D20))</f>
+        <f t="shared" si="3"/>
         <v>15300</v>
       </c>
       <c r="M20">
@@ -2173,34 +2178,34 @@
         <v>2.8560000000000002E-2</v>
       </c>
       <c r="Q20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.4618057142857144E-3</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="T20" s="2"/>
       <c r="W20" s="7"/>
     </row>
     <row r="21" spans="1:27" ht="17">
       <c r="A21" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21">
         <v>50</v>
       </c>
       <c r="C21">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D21">
         <v>0.3</v>
       </c>
       <c r="E21" s="12">
-        <f>IF(ISBLANK(#REF!), "", B21*C21)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F21" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A21, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.5</v>
       </c>
       <c r="G21" s="12">
@@ -2208,7 +2213,7 @@
         <v>0.5</v>
       </c>
       <c r="H21" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I21" s="12">
@@ -2224,7 +2229,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L21">
-        <f>IF(ISBLANK(#REF!),"", (E21*F21*H21*I21*J21*D21))</f>
+        <f t="shared" si="3"/>
         <v>16830</v>
       </c>
       <c r="M21">
@@ -2244,54 +2249,54 @@
         <v>3.1415999999999999E-2</v>
       </c>
       <c r="Q21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.2059897142857143E-3</v>
       </c>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="U21" t="s">
         <v>11</v>
       </c>
-      <c r="U21" t="s">
+      <c r="V21" t="s">
         <v>12</v>
       </c>
-      <c r="V21" t="s">
+      <c r="W21" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="X21" t="s">
         <v>13</v>
       </c>
-      <c r="W21" s="7" t="s">
+      <c r="Y21" t="s">
         <v>37</v>
       </c>
-      <c r="X21" t="s">
-        <v>14</v>
-      </c>
-      <c r="Y21" t="s">
+      <c r="Z21" t="s">
         <v>38</v>
       </c>
-      <c r="Z21" t="s">
+      <c r="AA21" t="s">
         <v>39</v>
-      </c>
-      <c r="AA21" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="22" spans="1:27">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B22">
         <v>50</v>
       </c>
       <c r="C22">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D22">
         <v>0.3</v>
       </c>
       <c r="E22" s="12">
-        <f>IF(ISBLANK(#REF!), "", B22*C22)</f>
+        <f t="shared" si="0"/>
         <v>100000</v>
       </c>
       <c r="F22" s="12">
-        <f>IF(ISBLANK(#REF!), "", VLOOKUP($A22, $S$22:$AA$39, 2, FALSE))</f>
+        <f t="shared" si="1"/>
         <v>1.46</v>
       </c>
       <c r="G22" s="12">
@@ -2299,7 +2304,7 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="I22" s="12">
@@ -2315,7 +2320,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="L22">
-        <f>IF(ISBLANK(#REF!),"", (E22*F22*H22*I22*J22*D22))</f>
+        <f t="shared" si="3"/>
         <v>16381.199999999999</v>
       </c>
       <c r="M22">
@@ -2335,11 +2340,11 @@
         <v>3.0578239999999996E-2</v>
       </c>
       <c r="Q22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="4"/>
         <v>1.1738299885714284E-3</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="T22" s="11">
         <v>1.5</v>
@@ -2369,7 +2374,7 @@
     <row r="23" spans="1:27">
       <c r="A23" s="2"/>
       <c r="S23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="T23" s="11">
         <v>1.24</v>
@@ -2399,7 +2404,7 @@
     <row r="24" spans="1:27">
       <c r="A24" s="2"/>
       <c r="S24" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T24" s="11">
         <v>0.81</v>
@@ -2432,7 +2437,7 @@
         <v/>
       </c>
       <c r="S25" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="T25" s="11">
         <v>1.42</v>
@@ -2465,7 +2470,7 @@
         <v/>
       </c>
       <c r="S26" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="T26" s="11">
         <v>1.31</v>
@@ -2498,7 +2503,7 @@
         <v/>
       </c>
       <c r="S27" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="T27" s="11">
         <v>1.5</v>
@@ -2531,7 +2536,7 @@
         <v/>
       </c>
       <c r="S28" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="T28" s="11">
         <v>1.5</v>
@@ -2560,7 +2565,7 @@
     </row>
     <row r="29" spans="1:27">
       <c r="S29" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="T29" s="11">
         <v>1.46</v>
@@ -2589,7 +2594,7 @@
     </row>
     <row r="30" spans="1:27">
       <c r="S30" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="T30" s="11">
         <v>1.37</v>
@@ -2618,7 +2623,7 @@
     </row>
     <row r="31" spans="1:27">
       <c r="S31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="T31" s="11">
         <v>0.34</v>
@@ -2639,7 +2644,7 @@
         <v>0.01</v>
       </c>
       <c r="Z31" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA31" s="10">
         <v>0.85</v>
@@ -2647,7 +2652,7 @@
     </row>
     <row r="32" spans="1:27">
       <c r="S32" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T32" s="11">
         <v>1.07</v>
@@ -2676,7 +2681,7 @@
     </row>
     <row r="33" spans="19:27">
       <c r="S33" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="T33" s="11">
         <v>0.25</v>
@@ -2705,7 +2710,7 @@
     </row>
     <row r="34" spans="19:27">
       <c r="S34" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T34" s="11">
         <v>1.9</v>
@@ -2726,7 +2731,7 @@
         <v>0.01</v>
       </c>
       <c r="Z34" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA34" s="10">
         <v>0.85</v>
@@ -2734,7 +2739,7 @@
     </row>
     <row r="35" spans="19:27">
       <c r="S35" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="T35" s="11">
         <v>1.5</v>
@@ -2752,10 +2757,10 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="Y35" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Z35" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA35" s="10">
         <v>0.85</v>
@@ -2763,7 +2768,7 @@
     </row>
     <row r="36" spans="19:27">
       <c r="S36" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="T36" s="11">
         <v>2.08</v>
@@ -2792,7 +2797,7 @@
     </row>
     <row r="37" spans="19:27">
       <c r="S37" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="T37" s="11">
         <v>1.34</v>
@@ -2813,7 +2818,7 @@
         <v>0.01</v>
       </c>
       <c r="Z37" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AA37" s="10">
         <v>0.85</v>
@@ -2821,7 +2826,7 @@
     </row>
     <row r="38" spans="19:27">
       <c r="S38" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T38" s="9">
         <v>1</v>
@@ -2842,15 +2847,15 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="Z38" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA38" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="39" spans="19:27">
       <c r="S39" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="T39" s="9">
         <v>1.5</v>
@@ -2868,13 +2873,13 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="Y39" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z39" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AA39" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="40" spans="19:27">
